--- a/calendar_chilean_2023A.xlsx
+++ b/calendar_chilean_2023A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed268546/Dropbox/Mac/Documents/codes/SPOCK_chilean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2753B0E8-FAB3-8B46-BD13-656F8EDC8428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F05327-F6EB-864A-9C67-7D93EA8D6670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22600" yWindow="500" windowWidth="28600" windowHeight="20840" xr2:uid="{29A8BF1E-0110-C24B-9407-C010B9269ACA}"/>
+    <workbookView xWindow="9800" yWindow="500" windowWidth="28600" windowHeight="20840" xr2:uid="{29A8BF1E-0110-C24B-9407-C010B9269ACA}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -5355,7 +5355,10 @@
         <v>66</v>
       </c>
       <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
+      <c r="H185">
+        <f>COUNTIF(H1:H184,"sent 1 week in advance")</f>
+        <v>9</v>
+      </c>
       <c r="I185">
         <f>COUNTIF(I1:I184,"True")</f>
         <v>42</v>
@@ -5364,12 +5367,18 @@
     <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F186" s="4"/>
       <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
+      <c r="H186">
+        <f>COUNTIF(H2:H185,"sent 2 weeks in advance")</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F187" s="4"/>
       <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
+      <c r="H187">
+        <f>COUNTIF(H3:H186,"sent 3 days in advance")</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F188" s="4"/>
